--- a/转换稿/《上海电子仪表工业志》1999 第一章.xlsx
+++ b/转换稿/《上海电子仪表工业志》1999 第一章.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待核" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fact and Comp-Beijing" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semi-Product" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comp-Product" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Name-History" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="待核" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Fact and Comp-Shanghai" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Semi-Product" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Comp-Product" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Name-History" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -611,7 +611,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>东海系列微型计算机、TQ一5机、TQ-16中型通用计算机、大型计算机</t>
+          <t>DJS-054微型计算机、东海0530B微型计算机、东海0540B微型计算机、东海系列微型计算机</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -619,7 +619,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>由上海无线电仪器厂-&gt;19800000改名上海电子计算机厂</t>
+          <t>上海无线电仪器厂-&gt;19800000改名上海电子计算机厂</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>王安CCS个人电脑、VS系列超级小型机、JDK一331型工业控制机</t>
+          <t>王安CCS个人电脑、VS系列超级小型机、JDK-331型工业控制机</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -910,7 +910,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>电子计算机、655大型计算机、厚膜电路、运载火箭的箭载计算机</t>
+          <t>电子计算机、M0572加固型微型计算机、655大型计算机、厚膜电路</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -946,7 +946,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1966年6月，建立国内最早专业生产电子计算机工厂——上海无线电十三厂，这是计算机科研成果转化为工业生产，并为上海计算机工业的发展迈出了重要一步。 ⏐ 1969年2月，上海无线电十三厂开始接产655大型计算机，以华东计算技术研究所研制的655科研样机为基础，应用户要求作了较大的改动，重新进行设计，定名为TQ一6型计算机。</t>
+          <t>1966年6月，建立国内最早专业生产电子计算机工厂——上海无线电十三厂，这是计算机科研成果转化为工业生产，并为上海计算机工业的发展迈出了重要一步。</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -965,17 +965,13 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>TQ一16中型通用数字集成电路计算机、J一101型计算机、专用电子计算机、TQ-21型数据处理机</t>
+          <t>TQ-16中型通用数字集成电路计算机、J-101型计算机、专用电子计算机、TQ-21型数据处理机</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>19660600</v>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>19690200改名TQ一6型计算机</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
@@ -1010,7 +1006,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1973年，该机正式由上海长宁拉手厂投产，并命名为CJ一709型计算机。</t>
+          <t>1973年，该机正式由上海长宁拉手厂投产，并命名为CJ-709型计算机。</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1061,7 +1057,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1980年12月，上海长江电子计算机厂和上海工业大学合作，采用上海无线电十四厂研制成功的四片微处理器芯片，试制成功上海地区第一台全国产器件的字长为8位的DJS一051微型计算机； ⏐ 1980年12月，上海长江电子计算机厂和上海工业大学合作，采用上海无线电十四厂研制生产的国产四片微处理器芯片，开发成功字长为8位的DJS—051微型计算机，这是上海地区开发成功的第一台自行设计和采用国产元器件组成的微型计算机，共生产134台，并率先在国防、工业控制中得到初步应用。</t>
+          <t>1980年12月，上海长江电子计算机厂和上海工业大学合作，采用上海无线电十四厂研制成功的四片微处理器芯片，试制成功上海地区第一台全国产器件的字长为8位的DJS-051微型计算机； ⏐ 1980年12月，上海长江电子计算机厂和上海工业大学合作，采用上海无线电十四厂研制生产的国产四片微处理器芯片，开发成功字长为8位的DJS—051微型计算机，这是上海地区开发成功的第一台自行设计和采用国产元器件组成的微型计算机，共生产134台，并率先在国防、工业控制中得到初步应用。</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1071,7 +1067,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>CJ-801单板微型机</t>
+          <t>DJS-051微型计算机、微型计算机、CJ-801单板微型机</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1095,7 +1091,7 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>上海市计算技术研究所</t>
+          <t>上海工业大学</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -1109,17 +1105,17 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>同期，上海市计算技术研究所试制成功DJS—056微型计算机，上海交通大学试制成功DJS一053微型计算机，上海工业自动化仪表研究所试制成功DJS一052E微型计算机，还有单位开发生产单板微型计算机。 ⏐ 期问，华东计算技术研究所和上海市计算技术研究所也派员参加了部分工作。</t>
+          <t>1980年12月，上海长江电子计算机厂和上海工业大学合作，采用上海无线电十四厂研制成功的四片微处理器芯片，试制成功上海地区第一台全国产器件的字长为8位的DJS-051微型计算机； ⏐ 1980年12月，上海长江电子计算机厂和上海工业大学合作，采用上海无线电十四厂研制生产的国产四片微处理器芯片，开发成功字长为8位的DJS—051微型计算机，这是上海地区开发成功的第一台自行设计和采用国产元器件组成的微型计算机，共生产134台，并率先在国防、工业控制中得到初步应用。</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>研究所</t>
+          <t>电子计算机</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DJS一053微型计算机、DJS一052E微型计算机、生产单板微型计算机、单板微型计算机</t>
+          <t>DJS-051微型计算机、微型计算机</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1127,7 +1123,7 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1143,7 +1139,7 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>上海交通大学</t>
+          <t>上海无线电十四厂</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
@@ -1157,7 +1153,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>同期，上海市计算技术研究所试制成功DJS—056微型计算机，上海交通大学试制成功DJS一053微型计算机，上海工业自动化仪表研究所试制成功DJS一052E微型计算机，还有单位开发生产单板微型计算机。 ⏐ 1958年，上海市人民政府有关部门组织华东计算技术研究所、上海有线电厂、复旦大学、上海交通大学、华东师范大学等单位的技术力量，对电子管计算机进行研制。</t>
+          <t>1980年12月，上海长江电子计算机厂和上海工业大学合作，采用上海无线电十四厂研制成功的四片微处理器芯片，试制成功上海地区第一台全国产器件的字长为8位的DJS-051微型计算机； ⏐ 1980年12月，上海长江电子计算机厂和上海工业大学合作，采用上海无线电十四厂研制生产的国产四片微处理器芯片，开发成功字长为8位的DJS—051微型计算机，这是上海地区开发成功的第一台自行设计和采用国产元器件组成的微型计算机，共生产134台，并率先在国防、工业控制中得到初步应用。</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1167,7 +1163,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>DJS一053微型计算机、DJS一052E微型计算机、生产单板微型计算机、单板微型计算机</t>
+          <t>DJS-051微型计算机、微型计算机</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1191,7 +1187,7 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>上海工业自动化仪表研究所</t>
+          <t>上海市计算技术研究所</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
@@ -1205,7 +1201,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>同期，上海市计算技术研究所试制成功DJS—056微型计算机，上海交通大学试制成功DJS一053微型计算机，上海工业自动化仪表研究所试制成功DJS一052E微型计算机，还有单位开发生产单板微型计算机。 ⏐ 80年代初期，相继开发成功的还有上海计算技术研究所的DJS—056微型计算机、上海交通大学的DJS一053微型计算机、上海工业自动化仪表研究所的DJS—052E微型计算机。</t>
+          <t>同期，上海市计算技术研究所试制成功DJS—056微型计算机，上海交通大学试制成功DJS-053微型计算机，上海工业自动化仪表研究所试制成功DJS-052E微型计算机，还有单位开发生产单板微型计算机。 ⏐ 期问，华东计算技术研究所和上海市计算技术研究所也派员参加了部分工作。</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1215,7 +1211,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>DJS一053微型计算机、DJS一052E微型计算机、生产单板微型计算机、单板微型计算机</t>
+          <t>DJS-053微型计算机、DJS-052E微型计算机、生产单板微型计算机、单板微型计算机</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1239,7 +1235,7 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>复旦大学</t>
+          <t>上海交通大学</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -1248,12 +1244,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·1. 电子管计算机</t>
+          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1958年，上海市人民政府有关部门组织华东计算技术研究所、上海有线电厂、复旦大学、上海交通大学、华东师范大学等单位的技术力量，对电子管计算机进行研制。 ⏐ 1971年8月，上海长宁拉手厂、上海市计算中心、复旦大学实行厂、所、校三结合试制第二台709型计算机，并于1972年完成。</t>
+          <t>同期，上海市计算技术研究所试制成功DJS—056微型计算机，上海交通大学试制成功DJS-053微型计算机，上海工业自动化仪表研究所试制成功DJS-052E微型计算机，还有单位开发生产单板微型计算机。 ⏐ 1958年，上海市人民政府有关部门组织华东计算技术研究所、上海有线电厂、复旦大学、上海交通大学、华东师范大学等单位的技术力量，对电子管计算机进行研制。</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1263,7 +1259,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>第二台709型计算机</t>
+          <t>DJS-053微型计算机、DJS-052E微型计算机、生产单板微型计算机、单板微型计算机</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1287,7 +1283,7 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>华东师范大学</t>
+          <t>上海工业自动化仪表研究所</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -1296,29 +1292,30 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·1. 电子管计算机</t>
+          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1973年开始，随着国内系列机的研制，系统软件的开发也加快了步伐，第四机械工业部组织了软件联合设计组，并在华东师范大学设立了100系列计算机软件调试中心，上海无电线十三厂又在DJS一131计算机上增加了实时操作系统（RTOS）的相应模块，对实时磁盘操作系统RDOS进行研究使用。</t>
+          <t>同期，上海市计算技术研究所试制成功DJS—056微型计算机，上海交通大学试制成功DJS-053微型计算机，上海工业自动化仪表研究所试制成功DJS-052E微型计算机，还有单位开发生产单板微型计算机。 ⏐ 80年代初期，相继开发成功的还有上海计算技术研究所的DJS—056微型计算机、上海交通大学的DJS-053微型计算机、上海工业自动化仪表研究所的DJS—052E微型计算机。</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>电子计算机</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="n">
-        <v>19730000</v>
+          <t>研究所</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>DJS-053微型计算机、DJS-052E微型计算机、生产单板微型计算机、单板微型计算机</t>
+        </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -1334,7 +1331,7 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>美国IBM公司</t>
+          <t>复旦大学</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -1343,12 +1340,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·1. 东海系列微型计算机</t>
+          <t>上海电子仪表工业志·第一章电子计算机·1. 电子管计算机</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>上海计算机工业的建立，引起国际同行的关注，上海电子计算机厂便成为国外了解中国高科技企业的窗口，1966～1980年，美国IBM公司董事长、日本富士通株式会社董事长等30多个国家和地区448批1412名学者、科学家、教授、企业家、记者等人士来该厂考察和参观。</t>
+          <t>1958年，上海市人民政府有关部门组织华东计算技术研究所、上海有线电厂、复旦大学、上海交通大学、华东师范大学等单位的技术力量，对电子管计算机进行研制。 ⏐ 1971年8月，上海长宁拉手厂、上海市计算中心、复旦大学实行厂、所、校三结合试制第二台709型计算机，并于1972年完成。</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1356,9 +1353,10 @@
           <t>电子计算机</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="n">
-        <v>19660000</v>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>第二台709型计算机</t>
+        </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
@@ -1381,7 +1379,7 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>上海元件五厂</t>
+          <t>华东师范大学</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -1390,12 +1388,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+          <t>上海电子仪表工业志·第一章电子计算机·1. 电子管计算机</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>研制655大型计算机，首要关键是集成电路，上海市于1965年底集中了中国科学院冶金研究所、上海元件五厂、华东计算技术研究所等有关单位的技术人员组成了研制、生产、使用三结合小组。</t>
+          <t>1973年开始，随着国内系列机的研制，系统软件的开发也加快了步伐，第四机械工业部组织了软件联合设计组，并在华东师范大学设立了100系列计算机软件调试中心，上海无电线十三厂又在DJS-131计算机上增加了实时操作系统（RTOS）的相应模块，对实时磁盘操作系统RDOS进行研究使用。</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1403,10 +1401,9 @@
           <t>电子计算机</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>655大型计算机</t>
-        </is>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>19730000</v>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
@@ -1429,7 +1426,7 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>中国人民解放军总参谋部第五十六研究所</t>
+          <t>清华大学</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -1438,22 +1435,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+          <t>上海电子仪表工业志·第一章电子计算机·1. 东海系列微型计算机</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>该机于1967年由中国人民解放军总参谋部第五十六研究所研制，上海无线电十三厂参加了研制工作。 ⏐ 上海中兴无线电厂在中国人民解放军总参谋部第五十六研究所和上海无线电十三厂帮助下，也生产了J一101型计算机。</t>
+          <t>1981年7月，上海电子计算机厂在电子工业部第六研究所和清华大学的支持下，研制成功以INTEL8080为CPU的DJS-054微型计算机。 ⏐ 同年5月，在清华大学召开100系列计算机的方案论证会，并确定国内自行设计的100系列机的第一个机型为DJS—130小型计算机。</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>研究所</t>
+          <t>电子计算机</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>J一101型计算机</t>
+          <t>DJS-054微型计算机</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1461,7 +1458,7 @@
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -1477,21 +1474,21 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>上海工业大学</t>
+          <t>美国IBM公司</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.17</v>
+        <v>0.33</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
+          <t>上海电子仪表工业志·第一章电子计算机·1. 东海系列微型计算机</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1980年12月，上海长江电子计算机厂和上海工业大学合作，采用上海无线电十四厂研制成功的四片微处理器芯片，试制成功上海地区第一台全国产器件的字长为8位的DJS一051微型计算机； ⏐ 1980年12月，上海长江电子计算机厂和上海工业大学合作，采用上海无线电十四厂研制生产的国产四片微处理器芯片，开发成功字长为8位的DJS—051微型计算机，这是上海地区开发成功的第一台自行设计和采用国产元器件组成的微型计算机，共生产134台，并率先在国防、工业控制中得到初步应用。</t>
+          <t>上海计算机工业的建立，引起国际同行的关注，上海电子计算机厂便成为国外了解中国高科技企业的窗口，1966～1980年，美国IBM公司董事长、日本富士通株式会社董事长等30多个国家和地区448批1412名学者、科学家、教授、企业家、记者等人士来该厂考察和参观。</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1500,6 +1497,9 @@
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="n">
+        <v>19660000</v>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
@@ -1521,21 +1521,21 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>上海无线电十四厂</t>
+          <t>上海元件五厂</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.17</v>
+        <v>0.33</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
+          <t>上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1980年12月，上海长江电子计算机厂和上海工业大学合作，采用上海无线电十四厂研制成功的四片微处理器芯片，试制成功上海地区第一台全国产器件的字长为8位的DJS一051微型计算机； ⏐ 1980年12月，上海长江电子计算机厂和上海工业大学合作，采用上海无线电十四厂研制生产的国产四片微处理器芯片，开发成功字长为8位的DJS—051微型计算机，这是上海地区开发成功的第一台自行设计和采用国产元器件组成的微型计算机，共生产134台，并率先在国防、工业控制中得到初步应用。</t>
+          <t>研制655大型计算机，首要关键是集成电路，上海市于1965年底集中了中国科学院冶金研究所、上海元件五厂、华东计算技术研究所等有关单位的技术人员组成了研制、生产、使用三结合小组。</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1543,7 +1543,11 @@
           <t>电子计算机</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>655大型计算机</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
@@ -1565,35 +1569,39 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>联合公司</t>
+          <t>中国人民解放军总参谋部第五十六研究所</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.17</v>
+        <v>0.33</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
+          <t>上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>在产品不断更新换代的同时，工艺技术和生产能力也得到了相应的发展，长江计算机（集团）联合公司所属上海电子计算机厂通过“七五”技术改造，形成了一条年产能力达万台的微型计算机生产线，微型计算机的产量、产值和销售收入均有较大幅度增长，应用范围渗透到了社会各个领域，并初步形成一支从事微型计算机科研、开发、生产、销售、服务的专业 ⏐ 为进一步适应机械、电子、建筑、造船、航空等领域计算机辅助设计和辅助制造的需要，1989年，上海市科委向长江计算机（集团）联合公司下达了上海市“七五”重点科技开发项目东海WS—386型32位微机工程工作站的科技开发任务。</t>
+          <t>该机于1967年由中国人民解放军总参谋部第五十六研究所研制，上海无线电十三厂参加了研制工作。 ⏐ 上海中兴无线电厂在中国人民解放军总参谋部第五十六研究所和上海无线电十三厂帮助下，也生产了J-101型计算机。</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>电子计算机</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>研究所</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>J-101型计算机</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -1609,7 +1617,7 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>上海市无线电技术研究所</t>
+          <t>联合公司</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
@@ -1618,17 +1626,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·2. 晶体管计算机</t>
+          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>TQ一1型工业控制计算机1967年初，由上海无线电十三厂设计、华东计算技术研究所和上海市无线电技术研究所派员参加设计工作的TQ一1型机，为一台二进制、定点、通用的晶体管数字计算机，用作工业控制。 ⏐ 与此同时，上海市无线电技术研究所研制出晶体管直接数字控制仪（DDC)，用于上海炼油厂的减压装置。</t>
+          <t>在产品不断更新换代的同时，工艺技术和生产能力也得到了相应的发展，长江计算机（集团）联合公司所属上海电子计算机厂通过“七五”技术改造，形成了一条年产能力达万台的微型计算机生产线，微型计算机的产量、产值和销售收入均有较大幅度增长，应用范围渗透到了社会各个领域，并初步形成一支从事微型计算机科研、开发、生产、销售、服务的专业 ⏐ 为进一步适应机械、电子、建筑、造船、航空等领域计算机辅助设计和辅助制造的需要，1989年，上海市科委向长江计算机（集团）联合公司下达了上海市“七五”重点科技开发项目东海WS—386型32位微机工程工作站的科技开发任务。</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>研究所</t>
+          <t>电子计算机</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -1637,7 +1645,7 @@
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -1653,7 +1661,7 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>清华大学</t>
+          <t>上海市无线电技术研究所</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
@@ -1662,17 +1670,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·1. 东海系列微型计算机</t>
+          <t>上海电子仪表工业志·第一章电子计算机·2. 晶体管计算机</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1981年7月，上海电子计算机厂在电子工业部第六研究所和清华大学的支持下，研制成功以INTEL8080为CPU的DJS一054微型计算机。 ⏐ 同年5月，在清华大学召开100系列计算机的方案论证会，并确定国内自行设计的100系列机的第一个机型为DJS—130小型计算机。</t>
+          <t>TQ-1型工业控制计算机1967年初，由上海无线电十三厂设计、华东计算技术研究所和上海市无线电技术研究所派员参加设计工作的TQ-1型机，为一台二进制、定点、通用的晶体管数字计算机，用作工业控制。 ⏐ 与此同时，上海市无线电技术研究所研制出晶体管直接数字控制仪（DDC)，用于上海炼油厂的减压装置。</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>电子计算机</t>
+          <t>研究所</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -1681,7 +1689,7 @@
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -1799,7 +1807,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>上海在参加北京联合设计的同时，于1973年6月又组织了以上海无线电十三厂为主，有复旦大学、上海交通大学、吴泾化工厂、新安电工厂、上海自动化仪表研究所、浙江大学、长沙国防科技大学、上海师范大学、上海科技大学、上海中兴无线电厂等11家单位参加的DJS一131小型多功能电子计算机联合设计。 ⏐ 以后上海中兴无线电厂、新安电工厂等也投入生产，共生产73台。</t>
+          <t>上海在参加北京联合设计的同时，于1973年6月又组织了以上海无线电十三厂为主，有复旦大学、上海交通大学、吴泾化工厂、新安电工厂、上海自动化仪表研究所、浙江大学、长沙国防科技大学、上海师范大学、上海科技大学、上海中兴无线电厂等11家单位参加的DJS-131小型多功能电子计算机联合设计。 ⏐ 以后上海中兴无线电厂、新安电工厂等也投入生产，共生产73台。</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1887,7 +1895,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>与此同时，上海市无线电技术研究所研制出晶体管直接数字控制仪（DDC)，用于上海炼油厂的减压装置。 ⏐ 上海自动化仪表研究所研制的JDK一331型工业控制机，用于上海炼油厂的常压蒸馏装置等。</t>
+          <t>与此同时，上海市无线电技术研究所研制出晶体管直接数字控制仪（DDC)，用于上海炼油厂的减压装置。 ⏐ 上海自动化仪表研究所研制的JDK-331型工业控制机，用于上海炼油厂的常压蒸馏装置等。</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -1927,7 +1935,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>黄浦仪器厂自1964年起，开发和生产691（ZLJ—1）、693（09-1）、694（上游二号）、696（ZLS一2）、697（ZST—2）、841（ZST-2D）等机电式指挥仪后，为进一步加快产品更新换代速度，适应新技术发展趋势和用户的客观需要，该厂于1983年5月正式承接中国船舶工业</t>
+          <t>黄浦仪器厂自1964年起，开发和生产691（ZLJ—1）、693（09-1）、694（上游二号）、696（ZLS-2）、697（ZST—2）、841（ZST-2D）等机电式指挥仪后，为进一步加快产品更新换代速度，适应新技术发展趋势和用户的客观需要，该厂于1983年5月正式承接中国船舶工业</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -2116,7 +2124,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>东海系列微型计算机、TQ一5机、TQ-16中型通用计算机、大型计算机</t>
+          <t>DJS-054微型计算机、东海0530B微型计算机、东海0540B微型计算机、东海系列微型计算机</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -2124,12 +2132,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>由上海无线电仪器厂-&gt;19800000改名上海电子计算机厂</t>
+          <t>上海无线电仪器厂-&gt;19800000改名上海电子计算机厂</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2196,7 +2204,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -2253,7 +2261,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2301,7 +2309,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>王安CCS个人电脑、VS系列超级小型机、JDK一331型工业控制机</t>
+          <t>王安CCS个人电脑、VS系列超级小型机、JDK-331型工业控制机</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -2310,7 +2318,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2355,7 +2363,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>电子计算机、655大型计算机、厚膜电路、运载火箭的箭载计算机</t>
+          <t>电子计算机、M0572加固型微型计算机、655大型计算机、厚膜电路</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -2368,7 +2376,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -2397,20 +2405,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TQ一16中型通用数字集成电路计算机、J一101型计算机、专用电子计算机、TQ-21型数据处理机</t>
+          <t>TQ-16中型通用数字集成电路计算机、J-101型计算机、专用电子计算机、TQ-21型数据处理机</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>19660600</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>19690200改名TQ一6型计算机</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -2448,7 +2452,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -2477,13 +2481,13 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CJ-801单板微型机</t>
+          <t>DJS-051微型计算机、微型计算机、CJ-801单板微型机</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -2502,29 +2506,29 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>上海市计算技术研究所</t>
+          <t>上海工业大学</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>研究所</t>
+          <t>电子计算机</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DJS一053微型计算机、DJS一052E微型计算机、生产单板微型计算机、单板微型计算机</t>
+          <t>DJS-051微型计算机、微型计算机</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -2537,7 +2541,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>上海交通大学</t>
+          <t>上海无线电十四厂</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2547,13 +2551,13 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DJS一053微型计算机、DJS一052E微型计算机、生产单板微型计算机、单板微型计算机</t>
+          <t>DJS-051微型计算机、微型计算机</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -2572,7 +2576,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>上海工业自动化仪表研究所</t>
+          <t>上海市计算技术研究所</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2582,13 +2586,13 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DJS一053微型计算机、DJS一052E微型计算机、生产单板微型计算机、单板微型计算机</t>
+          <t>DJS-053微型计算机、DJS-052E微型计算机、生产单板微型计算机、单板微型计算机</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -2607,7 +2611,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>复旦大学</t>
+          <t>上海交通大学</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2617,13 +2621,13 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>第二台709型计算机</t>
+          <t>DJS-053微型计算机、DJS-052E微型计算机、生产单板微型计算机、单板微型计算机</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -2634,7 +2638,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·1. 电子管计算机</t>
+          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
         </is>
       </c>
       <c r="S14" t="inlineStr"/>
@@ -2642,33 +2646,34 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>华东师范大学</t>
+          <t>上海工业自动化仪表研究所</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>电子计算机</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="n">
-        <v>19730000</v>
+          <t>研究所</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>DJS-053微型计算机、DJS-052E微型计算机、生产单板微型计算机、单板微型计算机</t>
+        </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·1. 电子管计算机</t>
+          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
         </is>
       </c>
       <c r="S15" t="inlineStr"/>
@@ -2676,7 +2681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>美国IBM公司</t>
+          <t>复旦大学</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2684,14 +2689,15 @@
           <t>电子计算机</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="n">
-        <v>19660000</v>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>第二台709型计算机</t>
+        </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -2702,7 +2708,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·1. 东海系列微型计算机</t>
+          <t>上海电子仪表工业志·第一章电子计算机·1. 电子管计算机</t>
         </is>
       </c>
       <c r="S16" t="inlineStr"/>
@@ -2710,7 +2716,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>上海元件五厂</t>
+          <t>华东师范大学</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2718,15 +2724,14 @@
           <t>电子计算机</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>655大型计算机</t>
-        </is>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="n">
+        <v>19730000</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -2737,7 +2742,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+          <t>上海电子仪表工业志·第一章电子计算机·1. 电子管计算机</t>
         </is>
       </c>
       <c r="S17" t="inlineStr"/>
@@ -2745,34 +2750,34 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>中国人民解放军总参谋部第五十六研究所</t>
+          <t>清华大学</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>研究所</t>
+          <t>电子计算机</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>J一101型计算机</t>
+          <t>DJS-054微型计算机</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+          <t>上海电子仪表工业志·第一章电子计算机·1. 东海系列微型计算机</t>
         </is>
       </c>
       <c r="S18" t="inlineStr"/>
@@ -2780,7 +2785,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>上海工业大学</t>
+          <t>美国IBM公司</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2789,10 +2794,13 @@
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
+      <c r="D19" t="n">
+        <v>19660000</v>
+      </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -2803,7 +2811,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
+          <t>上海电子仪表工业志·第一章电子计算机·1. 东海系列微型计算机</t>
         </is>
       </c>
       <c r="S19" t="inlineStr"/>
@@ -2811,7 +2819,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>上海无线电十四厂</t>
+          <t>上海元件五厂</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2819,11 +2827,15 @@
           <t>电子计算机</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>655大型计算机</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -2834,7 +2846,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
+          <t>上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
         </is>
       </c>
       <c r="S20" t="inlineStr"/>
@@ -2842,30 +2854,34 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>联合公司</t>
+          <t>中国人民解放军总参谋部第五十六研究所</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>电子计算机</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>研究所</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>J-101型计算机</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
+          <t>上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
         </is>
       </c>
       <c r="S21" t="inlineStr"/>
@@ -2873,30 +2889,30 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>上海市无线电技术研究所</t>
+          <t>联合公司</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>研究所</t>
+          <t>电子计算机</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·2. 晶体管计算机</t>
+          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
         </is>
       </c>
       <c r="S22" t="inlineStr"/>
@@ -2904,30 +2920,30 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>清华大学</t>
+          <t>上海市无线电技术研究所</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>电子计算机</t>
+          <t>研究所</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·1. 东海系列微型计算机</t>
+          <t>上海电子仪表工业志·第一章电子计算机·2. 晶体管计算机</t>
         </is>
       </c>
       <c r="S23" t="inlineStr"/>
@@ -2947,7 +2963,7 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -2978,7 +2994,7 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -3009,7 +3025,7 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -3040,7 +3056,7 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -3067,7 +3083,7 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -3094,7 +3110,7 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -3286,7 +3302,7 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>推动了上海地区集成电路</t>
+          <t>TTL集成电路</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -3304,24 +3320,17 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>717晶体管</t>
+          <t>推动了上海地区集成电路</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>19680000</v>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。产量据「共生产35台」。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+          <t>研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M101"/>
+  <dimension ref="A1:M116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3454,7 +3463,7 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>655大型计算机</t>
+          <t>M0572加固型微型计算机</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -3465,21 +3474,17 @@
           <t>华东计算技术研究所</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>上海元件五厂</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>19650000</v>
+        <v>19871200</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+          <t>上海电子仪表工业志·第一章电子计算机·4. 加固型微型计算机</t>
         </is>
       </c>
     </row>
@@ -3487,7 +3492,7 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>运载火箭的箭载计算机</t>
+          <t>655大型计算机</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -3498,12 +3503,16 @@
           <t>华东计算技术研究所</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>上海元件五厂</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>19690000</v>
+        <v>19650000</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
@@ -3516,7 +3525,7 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KS一1箭载计算机</t>
+          <t>箭载计算机</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -3545,40 +3554,28 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TQ一16中型通用数字集成电路计算机</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>32768</t>
-        </is>
-      </c>
+          <t>KS-1箭载计算机</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>上海无线电十三厂</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>华东计算技术研究所</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>19730300</v>
+        <v>19690000</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>产量据「生产了153台」。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+          <t>上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
         </is>
       </c>
     </row>
@@ -3586,29 +3583,40 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>J一101型计算机</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+          <t>TQ-16中型通用数字集成电路计算机</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>32768</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>中国人民解放军总参谋部第五十六研究所</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>上海无线电十三厂</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
+      <c r="K7" t="n">
+        <v>19730300</v>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+          <t>产量据「生产了153台」。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
         </is>
       </c>
     </row>
@@ -3616,32 +3624,29 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>专用电子计算机</t>
+          <t>J-101型计算机</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>中国人民解放军总参谋部第五十六研究所</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>上海无线电十三厂</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="n">
-        <v>19740000</v>
-      </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>产量据「共生产97台」。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+          <t>上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
         </is>
       </c>
     </row>
@@ -3649,7 +3654,7 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TQ-21型数据处理机</t>
+          <t>专用电子计算机</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -3664,17 +3669,17 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>97</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>19770000</v>
+        <v>19740000</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>产量据「生产了25台」。上海电子仪表工业志·第一章电子计算机·4. 计算器</t>
+          <t>产量据「共生产97台」。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3687,7 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CJ-801单板微型机</t>
+          <t>TQ-21型数据处理机</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -3691,19 +3696,23 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>上海长江电子计算机厂</t>
+          <t>上海无线电十三厂</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>19830000</v>
+        <v>19770000</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·3. 单板微型计算机</t>
+          <t>产量据「生产了25台」。上海电子仪表工业志·第一章电子计算机·4. 计算器</t>
         </is>
       </c>
     </row>
@@ -3711,28 +3720,36 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>东海系列微型计算机</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>DJS-051微型计算机</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>上海工业大学</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>上海电子计算机厂</t>
+          <t>上海长江电子计算机厂、上海无线电十四厂</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>19840000</v>
+        <v>19801200</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·第三节生产技术·二、 工艺和设备</t>
+          <t>协作:上海工业大学、上海无线电十四厂。上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
         </is>
       </c>
     </row>
@@ -3740,32 +3757,40 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TQ一5机</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>微型计算机</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>上海工业大学</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>上海电子计算机厂</t>
+          <t>上海长江电子计算机厂、上海无线电十四厂</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>134</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
-        <v>19710000</v>
+        <v>19801200</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>产量据「先后生产15台」。上海电子仪表工业志·第一章电子计算机·第五节企业·一、 上海电子计算机厂</t>
+          <t>协作:上海工业大学、上海无线电十四厂。产量据「共生产134台」。上海电子仪表工业志·第一章电子计算机·1. 东海系列微型计算机</t>
         </is>
       </c>
     </row>
@@ -3773,7 +3798,7 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TQ-16中型通用计算机</t>
+          <t>CJ-801单板微型机</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -3782,23 +3807,19 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>上海电子计算机厂</t>
+          <t>上海长江电子计算机厂</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
-        <v>19730000</v>
+        <v>19830000</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>产量据「先后生产15台」。上海电子仪表工业志·第一章电子计算机·第五节企业·一、 上海电子计算机厂</t>
+          <t>上海电子仪表工业志·第一章电子计算机·3. 单板微型计算机</t>
         </is>
       </c>
     </row>
@@ -3806,7 +3827,7 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>大型计算机</t>
+          <t>DJS-054微型计算机</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -3819,19 +3840,15 @@
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>19740000</v>
+        <v>19810700</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>产量据「先后生产15台」。上海电子仪表工业志·第一章电子计算机·第五节企业·一、 上海电子计算机厂</t>
+          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
         </is>
       </c>
     </row>
@@ -3839,10 +3856,14 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DJS一131小型多功能通用计算机</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>东海0530B微型计算机</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
@@ -3852,19 +3873,15 @@
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
-        <v>19750000</v>
+        <v>19870700</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>产量据「先后生产15台」。上海电子仪表工业志·第一章电子计算机·第五节企业·一、 上海电子计算机厂</t>
+          <t>上海电子仪表工业志·第一章电子计算机·1. 东海系列微型计算机</t>
         </is>
       </c>
     </row>
@@ -3872,25 +3889,36 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DJS一053微型计算机</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>东海0540B微型计算机</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>上海市计算技术研究所</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>上海电子计算机厂</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>471</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
+      <c r="K16" t="n">
+        <v>19891200</v>
+      </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
+          <t>产量据「共生产471台」。上海电子仪表工业志·第一章电子计算机·1. 东海系列微型计算机</t>
         </is>
       </c>
     </row>
@@ -3898,25 +3926,28 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DJS一052E微型计算机</t>
+          <t>东海系列微型计算机</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>上海市计算技术研究所</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>上海电子计算机厂</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
+      <c r="K17" t="n">
+        <v>19840000</v>
+      </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
+          <t>上海电子仪表工业志·第一章电子计算机·第三节生产技术·二、 工艺和设备</t>
         </is>
       </c>
     </row>
@@ -3924,25 +3955,28 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>生产单板微型计算机</t>
+          <t>TQ-5机</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>上海市计算技术研究所</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>上海电子计算机厂</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
+      <c r="K18" t="n">
+        <v>19710000</v>
+      </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
+          <t>上海电子仪表工业志·第一章电子计算机·第五节企业·一、 上海电子计算机厂</t>
         </is>
       </c>
     </row>
@@ -3950,25 +3984,32 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>单板微型计算机</t>
+          <t>TQ-16中型通用计算机</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>上海市计算技术研究所</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>上海电子计算机厂</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
+      <c r="K19" t="n">
+        <v>19730000</v>
+      </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
+          <t>产量据「先后生产15台」。上海电子仪表工业志·第一章电子计算机·第五节企业·一、 上海电子计算机厂</t>
         </is>
       </c>
     </row>
@@ -3976,36 +4017,32 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>第二台709型计算机</t>
+          <t>大型计算机</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>上海市计算技术研究所</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>上海长宁拉手厂</t>
+          <t>上海电子计算机厂</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="n">
-        <v>19710800</v>
+        <v>19740000</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>产量据「共生产73台」。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+          <t>产量据「先后生产15台」。上海电子仪表工业志·第一章电子计算机·第五节企业·一、 上海电子计算机厂</t>
         </is>
       </c>
     </row>
@@ -4013,32 +4050,28 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>交通大学的DJS一053微型计算机</t>
+          <t>DJS-131小型多功能通用计算机</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>上海交通大学</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>上海电子计算机厂</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="n">
-        <v>19800000</v>
+        <v>19750000</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>产量据「共生产134台」。上海电子仪表工业志·第一章电子计算机·1. 东海系列微型计算机</t>
+          <t>上海电子仪表工业志·第一章电子计算机·第五节企业·一、 上海电子计算机厂</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4079,7 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>100B型等工业控制计算机</t>
+          <t>DJS-053微型计算机</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
@@ -4054,20 +4087,17 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>上海工业自动化仪表研究所</t>
+          <t>上海市计算技术研究所</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="n">
-        <v>19830000</v>
-      </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
         </is>
       </c>
     </row>
@@ -4075,32 +4105,25 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>型3种微型计算机</t>
+          <t>DJS-052E微型计算机</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>64K</t>
-        </is>
-      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>上海微电脑厂</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>上海市计算技术研究所</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="n">
-        <v>19870000</v>
-      </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·2. 长江微型计算机</t>
+          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
         </is>
       </c>
     </row>
@@ -4108,25 +4131,25 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>微型计算机和教育电脑</t>
+          <t>生产单板微型计算机</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>上海微电脑厂</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>上海市计算技术研究所</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·第五节企业·二、 上海微电脑厂</t>
+          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
         </is>
       </c>
     </row>
@@ -4134,28 +4157,25 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CJ-709中型集成电路计算机</t>
+          <t>单板微型计算机</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>上海微电脑厂</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>上海市计算技术研究所</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="n">
-        <v>19730000</v>
-      </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·第五节企业·二、 上海微电脑厂</t>
+          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
         </is>
       </c>
     </row>
@@ -4163,28 +4183,36 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CJ-1001中型集成电路计算机</t>
+          <t>第二台709型计算机</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>上海市计算技术研究所</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>上海微电脑厂</t>
+          <t>上海长宁拉手厂</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="n">
-        <v>19730000</v>
+        <v>19710800</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·第五节企业·二、 上海微电脑厂</t>
+          <t>产量据「共生产73台」。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
         </is>
       </c>
     </row>
@@ -4192,28 +4220,32 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DJS-051B微型机</t>
+          <t>DJS-053微型计算机</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>上海微电脑厂</t>
-        </is>
-      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>上海交通大学</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="n">
-        <v>19730000</v>
+        <v>19800000</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·第五节企业·二、 上海微电脑厂</t>
+          <t>产量据「共生产134台」。上海电子仪表工业志·第一章电子计算机·1. 东海系列微型计算机</t>
         </is>
       </c>
     </row>
@@ -4221,25 +4253,28 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>王安CCS个人电脑</t>
+          <t>100B型等工业控制计算机</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>上海王安电脑发展公司</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>上海工业自动化仪表研究所</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
+      <c r="K28" t="n">
+        <v>19830000</v>
+      </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·第五节企业·四、 上海王安电脑发展公司</t>
+          <t>上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
         </is>
       </c>
     </row>
@@ -4247,25 +4282,32 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>VS系列超级小型机</t>
+          <t>型3种微型计算机</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>64K</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>上海王安电脑发展公司</t>
+          <t>上海微电脑厂</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
+      <c r="K29" t="n">
+        <v>19870000</v>
+      </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·第五节企业·四、 上海王安电脑发展公司</t>
+          <t>上海电子仪表工业志·第一章电子计算机·2. 长江微型计算机</t>
         </is>
       </c>
     </row>
@@ -4273,33 +4315,25 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>JDK一331型工业控制机</t>
+          <t>微型计算机和教育电脑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>上海工业自动化仪表研究所</t>
-        </is>
-      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>上海王安电脑发展公司</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>上海炼油厂</t>
-        </is>
-      </c>
+          <t>上海微电脑厂</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·第五节企业·四、 上海王安电脑发展公司</t>
+          <t>上海电子仪表工业志·第一章电子计算机·第五节企业·二、 上海微电脑厂</t>
         </is>
       </c>
     </row>
@@ -4307,28 +4341,28 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>103型</t>
+          <t>CJ-709中型集成电路计算机</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>上海微电脑厂</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="n">
-        <v>19591200</v>
+        <v>19730000</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
+          <t>上海电子仪表工业志·第一章电子计算机·第五节企业·二、 上海微电脑厂</t>
         </is>
       </c>
     </row>
@@ -4336,32 +4370,28 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>属第二代的X一2型晶体管数字电子计算机</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
+          <t>CJ-1001中型集成电路计算机</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>25000</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>上海微电脑厂</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="n">
-        <v>19651200</v>
+        <v>19730000</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>研制单位未详。上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
+          <t>上海电子仪表工业志·第一章电子计算机·第五节企业·二、 上海微电脑厂</t>
         </is>
       </c>
     </row>
@@ -4369,24 +4399,28 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>101型</t>
+          <t>DJS-051B微型机</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>上海微电脑厂</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="n">
-        <v>19600000</v>
+        <v>19730000</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
+          <t>上海电子仪表工业志·第一章电子计算机·第五节企业·二、 上海微电脑厂</t>
         </is>
       </c>
     </row>
@@ -4394,24 +4428,25 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>10型</t>
+          <t>王安CCS个人电脑</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>上海王安电脑发展公司</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="n">
-        <v>19700000</v>
-      </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
+          <t>上海电子仪表工业志·第一章电子计算机·第五节企业·四、 上海王安电脑发展公司</t>
         </is>
       </c>
     </row>
@@ -4419,24 +4454,25 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>185小型计算机</t>
+          <t>VS系列超级小型机</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>上海王安电脑发展公司</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="n">
-        <v>19700000</v>
-      </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>研制单位未详。上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
+          <t>上海电子仪表工业志·第一章电子计算机·第五节企业·四、 上海王安电脑发展公司</t>
         </is>
       </c>
     </row>
@@ -4444,24 +4480,33 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>和开发属第四代计算机的微型计算机</t>
+          <t>JDK-331型工业控制机</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>上海工业自动化仪表研究所</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>上海王安电脑发展公司</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>上海炼油厂</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="n">
-        <v>19700000</v>
-      </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>研制单位未详。上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
+          <t>上海电子仪表工业志·第一章电子计算机·第五节企业·四、 上海王安电脑发展公司</t>
         </is>
       </c>
     </row>
@@ -4469,19 +4514,23 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>属第四代计算机的微型计算机</t>
+          <t>103型电子管计算机</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="n">
-        <v>19700000</v>
+        <v>19591200</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
@@ -4494,24 +4543,32 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>INTEL8080</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>X-2型晶体管数字电子计算机</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>25000</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="n">
-        <v>19810700</v>
+        <v>19651200</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
+          <t>研制单位未详。上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
         </is>
       </c>
     </row>
@@ -4519,7 +4576,7 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0540的东海系列微型计算机</t>
+          <t>10型</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -4530,10 +4587,13 @@
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
+      <c r="K39" t="n">
+        <v>19700000</v>
+      </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>研制单位未详。上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4601,7 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>地区第一台103型电子管数字计算机</t>
+          <t>集成电路计算机</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -4553,12 +4613,12 @@
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="n">
-        <v>19591200</v>
+        <v>19700000</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>研制单位未详。上海电子仪表工业志·第一章电子计算机·1. 电子管计算机</t>
+          <t>研制单位未详。上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
         </is>
       </c>
     </row>
@@ -4566,28 +4626,24 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>501型</t>
+          <t>185小型计算机</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>50000</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="n">
-        <v>19600000</v>
+        <v>19700000</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·1. 电子管计算机</t>
+          <t>研制单位未详。上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4651,7 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>3型晶体管计算机</t>
+          <t>DJS-184</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
@@ -4607,12 +4663,12 @@
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="n">
-        <v>19631000</v>
+        <v>19700000</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>研制单位未详。上海电子仪表工业志·第一章电子计算机·2. 晶体管计算机</t>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
         </is>
       </c>
     </row>
@@ -4620,7 +4676,7 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>905甲机</t>
+          <t>INTEL8080</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
@@ -4631,10 +4687,13 @@
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
+      <c r="K43" t="n">
+        <v>19810700</v>
+      </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·2. 晶体管计算机</t>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4701,7 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0540型</t>
+          <t>地区第一台103型电子管数字计算机</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -4654,12 +4713,12 @@
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="n">
-        <v>19850000</v>
+        <v>19591200</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·1. 东海系列微型计算机</t>
+          <t>研制单位未详。上海电子仪表工业志·第一章电子计算机·1. 电子管计算机</t>
         </is>
       </c>
     </row>
@@ -4667,32 +4726,28 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>INTEL8088</t>
+          <t>J-501型电子管计算机</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>256K</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>8142</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="n">
-        <v>19850000</v>
+        <v>19600000</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。产量据「共生产8142台」。上海电子仪表工业志·第一章电子计算机·1. 东海系列微型计算机</t>
+          <t>研制单位未详。上海电子仪表工业志·第一章电子计算机·1. 电子管计算机</t>
         </is>
       </c>
     </row>
@@ -4700,7 +4755,7 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>INTEL8028</t>
+          <t>3型晶体管计算机</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -4711,10 +4766,13 @@
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
+      <c r="K46" t="n">
+        <v>19631000</v>
+      </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·1. 东海系列微型计算机</t>
+          <t>研制单位未详。上海电子仪表工业志·第一章电子计算机·2. 晶体管计算机</t>
         </is>
       </c>
     </row>
@@ -4722,19 +4780,11 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>INTEL8038</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>X-1</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
@@ -4742,12 +4792,12 @@
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="n">
-        <v>19890000</v>
+        <v>19631000</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·1. 东海系列微型计算机</t>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·2. 晶体管计算机</t>
         </is>
       </c>
     </row>
@@ -4755,32 +4805,28 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>COMPAQ386</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>TQ-1型</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="n">
-        <v>19890000</v>
+        <v>19670000</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·1. 东海系列微型计算机</t>
+          <t>型号据字面认出,研制单位未详。产量据「共生产了3台」。上海电子仪表工业志·第一章电子计算机·2. 晶体管计算机</t>
         </is>
       </c>
     </row>
@@ -4788,7 +4834,7 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>C25</t>
+          <t>905甲机</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -4797,19 +4843,12 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>471</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
-      <c r="K49" t="n">
-        <v>19900000</v>
-      </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。产量据「共生产471台」。上海电子仪表工业志·第一章电子计算机·1. 东海系列微型计算机</t>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·2. 晶体管计算机</t>
         </is>
       </c>
     </row>
@@ -4817,24 +4856,33 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CJ-803</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
+          <t>S-100</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>48K</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr"/>
-      <c r="K50" t="n">
-        <v>19830000</v>
-      </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 单板微型计算机</t>
+          <t>型号据字面认出,研制单位未详。产量据「生产116台」。上海电子仪表工业志·第一章电子计算机·1. 东海系列微型计算机</t>
         </is>
       </c>
     </row>
@@ -4842,7 +4890,7 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CJ-804</t>
+          <t>0540型</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -4854,12 +4902,12 @@
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="n">
-        <v>19830000</v>
+        <v>19850000</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 单板微型计算机</t>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·1. 东海系列微型计算机</t>
         </is>
       </c>
     </row>
@@ -4867,25 +4915,32 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Z80</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
+          <t>INTEL8088</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>256K</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>8142</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr"/>
+      <c r="K52" t="n">
+        <v>19850000</v>
+      </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 单板微型计算机</t>
+          <t>型号据字面认出,研制单位未详。产量据「共生产8142台」。上海电子仪表工业志·第一章电子计算机·1. 东海系列微型计算机</t>
         </is>
       </c>
     </row>
@@ -4893,7 +4948,7 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>M0572</t>
+          <t>INTEL8028</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -4904,13 +4959,10 @@
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
-      <c r="K53" t="n">
-        <v>19871200</v>
-      </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·4. 加固型微型计算机</t>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·1. 东海系列微型计算机</t>
         </is>
       </c>
     </row>
@@ -4918,11 +4970,19 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>INTEL86</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
+          <t>INTEL8038</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
@@ -4930,12 +4990,12 @@
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="n">
-        <v>19871200</v>
+        <v>19890000</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·4. 加固型微型计算机</t>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·1. 东海系列微型计算机</t>
         </is>
       </c>
     </row>
@@ -4943,20 +5003,24 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>386型</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
+          <t>COMPAQ386</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="n">
         <v>19890000</v>
@@ -4964,7 +5028,7 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。产量据「生产14套」。上海电子仪表工业志·第一章电子计算机·5. 微机工程工作站</t>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·1. 东海系列微型计算机</t>
         </is>
       </c>
     </row>
@@ -4972,7 +5036,7 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ZST-2</t>
+          <t>C25</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -4981,15 +5045,19 @@
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>471</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="n">
-        <v>19640000</v>
+        <v>19900000</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·6. 典型应用系统及软件</t>
+          <t>型号据字面认出,研制单位未详。产量据「共生产471台」。上海电子仪表工业志·第一章电子计算机·1. 东海系列微型计算机</t>
         </is>
       </c>
     </row>
@@ -4997,7 +5065,7 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ZLQ-2</t>
+          <t>CJ-803</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -5006,19 +5074,15 @@
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="n">
-        <v>19850900</v>
+        <v>19830000</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。产量据「共生产7套」。上海电子仪表工业志·第一章电子计算机·6. 典型应用系统及软件</t>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 单板微型计算机</t>
         </is>
       </c>
     </row>
@@ -5026,7 +5090,7 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>INTEL8086</t>
+          <t>CJ-804</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -5037,10 +5101,13 @@
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
+      <c r="K58" t="n">
+        <v>19830000</v>
+      </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·6. 典型应用系统及软件</t>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 单板微型计算机</t>
         </is>
       </c>
     </row>
@@ -5048,10 +5115,14 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>成样机</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
+          <t>Z80</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
@@ -5062,7 +5133,7 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>研制单位未详。上海电子仪表工业志·第一章电子计算机·第三节生产技术·一、 设计：</t>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 单板微型计算机</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5141,7 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>905乙型</t>
+          <t>INTEL86</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -5081,10 +5152,13 @@
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
+      <c r="K60" t="n">
+        <v>19871200</v>
+      </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·第三节生产技术·一、 设计：</t>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·4. 加固型微型计算机</t>
         </is>
       </c>
     </row>
@@ -5092,7 +5166,7 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>655型</t>
+          <t>386型</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -5101,12 +5175,19 @@
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr"/>
+      <c r="K61" t="n">
+        <v>19890000</v>
+      </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·第三节生产技术·一、 设计：</t>
+          <t>型号据字面认出,研制单位未详。产量据「生产14套」。上海电子仪表工业志·第一章电子计算机·5. 微机工程工作站</t>
         </is>
       </c>
     </row>
@@ -5114,7 +5195,7 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>TQ-6</t>
+          <t>TQ-031</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -5125,10 +5206,13 @@
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
+      <c r="K62" t="n">
+        <v>19860000</v>
+      </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·第三节生产技术·三、 质量</t>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·6. 典型应用系统及软件</t>
         </is>
       </c>
     </row>
@@ -5136,7 +5220,7 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DJS一131小型多功能计算机</t>
+          <t>TQ-033</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -5148,12 +5232,12 @@
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="n">
-        <v>19750000</v>
+        <v>19860000</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>研制单位未详。上海电子仪表工业志·第一章电子计算机·第三节生产技术·三、 质量</t>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·6. 典型应用系统及软件</t>
         </is>
       </c>
     </row>
@@ -5161,7 +5245,7 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>709计算机</t>
+          <t>TQ-036</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -5170,19 +5254,15 @@
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="n">
-        <v>19770000</v>
+        <v>19890000</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。产量据「共生产47台」。上海电子仪表工业志·第一章电子计算机·第五节企业·二、 上海微电脑厂</t>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·6. 典型应用系统及软件</t>
         </is>
       </c>
     </row>
@@ -5190,7 +5270,7 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>VS500</t>
+          <t>WS-386型</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -5201,10 +5281,13 @@
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
+      <c r="K65" t="n">
+        <v>19900000</v>
+      </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·第五节企业·四、 上海王安电脑发展公司</t>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·6. 典型应用系统及软件</t>
         </is>
       </c>
     </row>
@@ -5212,7 +5295,7 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>VS800</t>
+          <t>ZLS-2</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -5223,10 +5306,13 @@
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
+      <c r="K66" t="n">
+        <v>19640000</v>
+      </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·第五节企业·四、 上海王安电脑发展公司</t>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·6. 典型应用系统及软件</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5320,7 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>331型</t>
+          <t>ZST-2</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -5245,10 +5331,13 @@
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
+      <c r="K67" t="n">
+        <v>19640000</v>
+      </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·第五节企业·四、 上海王安电脑发展公司</t>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·6. 典型应用系统及软件</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5345,7 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>DK一1型数字集成电路计算机</t>
+          <t>ZLQ-2</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -5265,15 +5354,19 @@
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="n">
-        <v>19690000</v>
+        <v>19850900</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+          <t>型号据字面认出,研制单位未详。产量据「共生产7套」。上海电子仪表工业志·第一章电子计算机·6. 典型应用系统及软件</t>
         </is>
       </c>
     </row>
@@ -5281,24 +5374,12 @@
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>DJS-131</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
-      </c>
+          <t>INTEL8086</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
@@ -5307,7 +5388,7 @@
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·6. 典型应用系统及软件</t>
         </is>
       </c>
     </row>
@@ -5315,7 +5396,7 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>DJS-130</t>
+          <t>TQTX-1</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -5326,10 +5407,13 @@
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
+      <c r="K70" t="n">
+        <v>19860000</v>
+      </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·6. 典型应用系统及软件</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5421,7 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>16型</t>
+          <t>M-103型</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -5346,16 +5430,12 @@
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。产量据「生产了153台」。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·第三节生产技术·一、 设计：</t>
         </is>
       </c>
     </row>
@@ -5363,7 +5443,7 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>数量最多的中型计算机</t>
+          <t>成样机</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -5372,16 +5452,12 @@
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>研制单位未详。产量据「生产了153台」。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+          <t>研制单位未详。上海电子仪表工业志·第一章电子计算机·第三节生产技术·一、 设计：</t>
         </is>
       </c>
     </row>
@@ -5389,32 +5465,21 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>运算速度达100万次的大型计算机</t>
+          <t>905乙型</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
-      </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
-      <c r="K73" t="n">
-        <v>19740400</v>
-      </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>研制单位未详。产量据「共生产了23台」。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·第三节生产技术·一、 设计：</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5487,7 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>220计算机</t>
+          <t>655型</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -5436,7 +5501,7 @@
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·第三节生产技术·一、 设计：</t>
         </is>
       </c>
     </row>
@@ -5444,7 +5509,7 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>260型</t>
+          <t>TQ-6型</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -5453,16 +5518,12 @@
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。产量据「生产了2台」。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·第三节生产技术·一、 设计：</t>
         </is>
       </c>
     </row>
@@ -5470,33 +5531,24 @@
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>第一台中型系列计算机</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>64K</t>
-        </is>
-      </c>
+          <t>101型</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
+      <c r="K76" t="n">
+        <v>19690000</v>
+      </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>研制单位未详。产量据「生产了2台」。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·第五节企业·一、 上海电子计算机厂</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5556,7 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>240型</t>
+          <t>CJ-9002</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -5518,7 +5570,7 @@
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·第五节企业·二、 上海微电脑厂</t>
         </is>
       </c>
     </row>
@@ -5526,7 +5578,7 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>并小批量生产的第三代集成电路计算机</t>
+          <t>VS500</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -5540,7 +5592,7 @@
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·第五节企业·四、 上海王安电脑发展公司</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5600,7 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>第三代集成电路计算机</t>
+          <t>VS800</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -5562,7 +5614,7 @@
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·第五节企业·四、 上海王安电脑发展公司</t>
         </is>
       </c>
     </row>
@@ -5570,7 +5622,7 @@
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>J-101型</t>
+          <t>DK-1型数字集成电路计算机</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -5581,10 +5633,13 @@
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
+      <c r="K80" t="n">
+        <v>19690000</v>
+      </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+          <t>研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
         </is>
       </c>
     </row>
@@ -5592,21 +5647,33 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TQ-11机</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr"/>
+          <t>DJS-130</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
       <c r="J81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+          <t>型号据字面认出,研制单位未详。产量据「共生产46台」。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
         </is>
       </c>
     </row>
@@ -5614,7 +5681,7 @@
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>905丙机</t>
+          <t>DJS-153</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -5625,6 +5692,9 @@
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
+      <c r="K82" t="n">
+        <v>19830000</v>
+      </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
@@ -5636,7 +5706,7 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>905型</t>
+          <t>709型</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -5648,7 +5718,7 @@
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="n">
-        <v>19790200</v>
+        <v>19700000</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
@@ -5661,7 +5731,7 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>成的717晶体管计算机</t>
+          <t>中型计算机</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -5672,17 +5742,14 @@
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>153</t>
         </is>
       </c>
       <c r="J84" t="inlineStr"/>
-      <c r="K84" t="n">
-        <v>19680000</v>
-      </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>研制单位未详。产量据「共生产35台」。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+          <t>研制单位未详。产量据「生产了153台」。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
         </is>
       </c>
     </row>
@@ -5690,7 +5757,7 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TQ一5型计算机</t>
+          <t>DJS-200</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -5699,19 +5766,15 @@
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="n">
-        <v>19710000</v>
+        <v>19730300</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>研制单位未详。产量据「生产了2台」。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
         </is>
       </c>
     </row>
@@ -5719,7 +5782,7 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>691计算机</t>
+          <t>DJS-220计算机</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -5730,9 +5793,6 @@
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
-      <c r="K86" t="n">
-        <v>19730000</v>
-      </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
@@ -5744,7 +5804,7 @@
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>KS一1A箭载计算机</t>
+          <t>220机</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -5755,13 +5815,10 @@
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
-      <c r="K87" t="n">
-        <v>19750000</v>
-      </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
         </is>
       </c>
     </row>
@@ -5769,7 +5826,7 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ZK45</t>
+          <t>260型</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -5778,15 +5835,16 @@
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J88" t="inlineStr"/>
-      <c r="K88" t="n">
-        <v>19840000</v>
-      </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+          <t>型号据字面认出,研制单位未详。产量据「生产了2台」。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
         </is>
       </c>
     </row>
@@ -5794,24 +5852,33 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>并投产的JS系列工业控制机</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr"/>
-      <c r="D89" t="inlineStr"/>
+          <t>第一台中型系列计算机</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>64K</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J89" t="inlineStr"/>
-      <c r="K89" t="n">
-        <v>19740000</v>
-      </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+          <t>研制单位未详。产量据「生产了2台」。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
         </is>
       </c>
     </row>
@@ -5819,7 +5886,7 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>JS系列工业控制机</t>
+          <t>DJS-240型</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -5830,13 +5897,10 @@
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
-      <c r="K90" t="n">
-        <v>19740000</v>
-      </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5908,7 @@
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>较高水平的TQ一3型工业控制机</t>
+          <t>第三代集成电路计算机</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -5866,7 +5930,7 @@
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>14型</t>
+          <t>TQ-11机</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -5875,19 +5939,12 @@
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
-      <c r="K92" t="n">
-        <v>19730000</v>
-      </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。产量据「共生产10台」。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
         </is>
       </c>
     </row>
@@ -5895,7 +5952,7 @@
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>19型</t>
+          <t>905丙机</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -5904,19 +5961,12 @@
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
-      <c r="K93" t="n">
-        <v>19740000</v>
-      </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。产量据「共生产97台」。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
         </is>
       </c>
     </row>
@@ -5924,7 +5974,7 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>12型</t>
+          <t>SB-75</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -5933,19 +5983,12 @@
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>24000</t>
-        </is>
-      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
-      <c r="K94" t="n">
-        <v>19720000</v>
-      </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。产量据「共生产24000多台」。上海电子仪表工业志·第一章电子计算机·4. 计算器</t>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
         </is>
       </c>
     </row>
@@ -5953,7 +5996,7 @@
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SC4332</t>
+          <t>905型</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -5965,12 +6008,12 @@
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="n">
-        <v>19840000</v>
+        <v>19790200</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·4. 计算器</t>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
         </is>
       </c>
     </row>
@@ -5978,7 +6021,7 @@
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>LF-8083</t>
+          <t>717晶体管计算机</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -5990,12 +6033,12 @@
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="n">
-        <v>19840000</v>
+        <v>19680000</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·4. 计算器</t>
+          <t>研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
         </is>
       </c>
     </row>
@@ -6003,7 +6046,7 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>300型</t>
+          <t>691计算机</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -6014,10 +6057,13 @@
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
+      <c r="K97" t="n">
+        <v>19730000</v>
+      </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·4. 计算器</t>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
         </is>
       </c>
     </row>
@@ -6025,21 +6071,36 @@
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>450型</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr"/>
+          <t>TQ-4</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J98" t="inlineStr"/>
+      <c r="K98" t="n">
+        <v>19730000</v>
+      </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·4. 计算器</t>
+          <t>型号据字面认出,研制单位未详。产量据「生产了1台」。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
         </is>
       </c>
     </row>
@@ -6047,7 +6108,7 @@
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>650型</t>
+          <t>ZK45</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -6058,10 +6119,13 @@
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
+      <c r="K99" t="n">
+        <v>19840000</v>
+      </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·4. 计算器</t>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
         </is>
       </c>
     </row>
@@ -6069,7 +6133,7 @@
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>203计算机</t>
+          <t>JS系列工业控制机</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -6078,19 +6142,15 @@
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="n">
-        <v>19770000</v>
+        <v>19740000</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>型号据字面认出,研制单位未详。产量据「生产了25台」。上海电子仪表工业志·第一章电子计算机·4. 计算器</t>
+          <t>研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
         </is>
       </c>
     </row>
@@ -6098,7 +6158,7 @@
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>131计算机</t>
+          <t>JDK-100</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -6110,10 +6170,380 @@
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="n">
-        <v>19780000</v>
+        <v>19830000</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>TQ-3型工业控制机</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>TQ-14型</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="n">
+        <v>19730000</v>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产10台」。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>TQ-19型</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="n">
+        <v>19740000</v>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产97台」。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>TQ-12型</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>24000</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="n">
+        <v>19720000</v>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产24000多台」。上海电子仪表工业志·第一章电子计算机·4. 计算器</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>12型</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·4. 计算器</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>SC4332</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="n">
+        <v>19840000</v>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·4. 计算器</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr"/>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>LF-8083</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="n">
+        <v>19840000</v>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·4. 计算器</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr"/>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>300型</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·4. 计算器</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>450型</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·4. 计算器</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr"/>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>650型</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·4. 计算器</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr"/>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>203计算机</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="n">
+        <v>19770000</v>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「生产了25台」。上海电子仪表工业志·第一章电子计算机·4. 计算器</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>YSJ-1</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·5. 典型应用系统及软件</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>SYJ-1</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·5. 典型应用系统及软件</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>131计算机</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="n">
+        <v>19780000</v>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·5. 典型应用系统及软件</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr"/>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>ALGOL-60</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="n">
+        <v>19700000</v>
+      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
         <is>
           <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·5. 典型应用系统及软件</t>
         </is>
@@ -6130,7 +6560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6139,6 +6569,7 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6149,139 +6580,161 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>序</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>单位(今名)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>From</t>
+          <t>当时名称</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>自哪年起</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Remark</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>↑ 一行 = 某单位某一段时间里叫什么。念法:「自哪年起」那一年起,这家单位叫「当时名称」那个名字,到下一行那年为止。「单位(今名)」是它如今的正名,一家单位的几行都写同一个 —— 那是钥匙,不是它当时的名字。「序」是这家单位的第几个名字,1 最早 —— 不是行号。两家单位并成一家,不在这张表里,写进「待核」表的「创办」列。</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>上海无线电十三厂</t>
-        </is>
+      <c r="B2" t="n">
+        <v>1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TQ一6型计算机</t>
+          <t>上海微电脑厂</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>19690200</t>
+          <t>上海长江电子计算机厂</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1969年2月，上海无线电十三厂开始接产655大型计算机，以华东计算技术研究所研制的655科研样机为基础，应用户要求作了较大的改动，重新进行设计，定名为TQ一6型计算机。</t>
+          <t>19800000</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
+          <t>1980年改名为上海长江电子计算机厂。</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>上海电子仪表工业志·第一章电子计算机·2. 长江微型计算机</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>上海电子计算机厂</t>
-        </is>
+      <c r="B3" t="n">
+        <v>2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>上海电子计算机厂</t>
+          <t>上海微电脑厂</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>19800000</t>
+          <t>上海微电脑厂</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1970年迁至南京西路1486号，1980年更名为上海电子计算机厂。</t>
+          <t>19840000</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
+          <t>1984年易名为上海微电脑厂，注册商标为CJ。</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>上海电子仪表工业志·第一章电子计算机·2. 长江微型计算机</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>上海微电脑厂</t>
-        </is>
+      <c r="B4" t="n">
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>上海长江电子计算机厂</t>
+          <t>上海电子计算机厂</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>上海电子计算机厂</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>19800000</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>1980年改名为上海长江电子计算机厂。</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·2. 长江微型计算机</t>
+          <t>1970年迁至南京西路1486号，1980年更名为上海电子计算机厂。</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>上海微电脑厂</t>
-        </is>
+      <c r="B5" t="n">
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>上海微电脑厂</t>
+          <t>上海电子计算机厂</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>上海无线电仪器厂</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>19840000</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1984年易名为上海微电脑厂，注册商标为CJ。</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·2. 长江微型计算机</t>
+          <t>始建时名称。其前身由上海无线电仪器厂6401新产品试制小组演变而成，厂址在胶州路397号。</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
         </is>
       </c>
     </row>
